--- a/files/CHR/talk_紫苑.xlsx
+++ b/files/CHR/talk_紫苑.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F2AD6B-C6DF-4B8E-A8C4-330349119547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87CCE55-A2BD-430D-90E2-9A2BF8B643C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="27990" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="525" windowWidth="27990" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="183">
   <si>
     <t>各キャラクタのランダムセリフ集。指定座標のセリフがあればそちらを優先してしゃべる。</t>
   </si>
@@ -554,6 +554,95 @@
     <t>うーん…何かいいものはないかな…</t>
     <rPh sb="4" eb="5">
       <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月21日主</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12月21日反応</t>
+    <rPh sb="2" eb="3">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドハント反応</t>
+    <rPh sb="7" eb="9">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨晩からずっと化け物の群れが絶えないね…</t>
+    <rPh sb="0" eb="2">
+      <t>サクバン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちょっと今は表出られないね…</t>
+    <rPh sb="4" eb="5">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オモテ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>デ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なんてことなの…化け物がこんなに…</t>
+    <rPh sb="8" eb="9">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もうここにもいられない…突っ切る！</t>
+    <rPh sb="12" eb="13">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -617,7 +706,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -637,6 +726,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -951,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.75" style="6" customWidth="1"/>
@@ -1718,51 +1810,51 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
-        <v>137</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>138</v>
+      <c r="A97" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
-        <v>139</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>140</v>
+      <c r="A98" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
-        <v>141</v>
+      <c r="A99" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
-        <v>141</v>
+      <c r="A100" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="B100" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>141</v>
-      </c>
-      <c r="B101" t="s">
-        <v>144</v>
+        <v>137</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>141</v>
-      </c>
-      <c r="B102" t="s">
-        <v>145</v>
+        <v>139</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
@@ -1770,7 +1862,7 @@
         <v>141</v>
       </c>
       <c r="B103" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
@@ -1778,174 +1870,206 @@
         <v>141</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>141</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>148</v>
+      <c r="B105" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B106" s="1"/>
+      <c r="A106" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>149</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
+      </c>
+      <c r="B107" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>149</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
+      </c>
+      <c r="B108" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>141</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
-        <v>152</v>
-      </c>
-      <c r="B110" t="s">
-        <v>153</v>
-      </c>
+      <c r="B110" s="1"/>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>152</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
         <v>152</v>
       </c>
-      <c r="B112" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>152</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>156</v>
+      <c r="B114" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>157</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
+      </c>
+      <c r="B116" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
+        <v>152</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
         <v>157</v>
       </c>
-      <c r="B117" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A118" t="s">
-        <v>157</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>161</v>
+      <c r="B119" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>162</v>
-      </c>
-      <c r="B121" t="s">
-        <v>164</v>
+        <v>157</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
+        <v>157</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
         <v>162</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A123" t="s">
-        <v>162</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>166</v>
+      <c r="B124" s="4" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>167</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
+      </c>
+      <c r="B125" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>167</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>167</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
-        <v>167</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>167</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>167</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B130" s="2"/>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B134" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/files/CHR/talk_紫苑.xlsx
+++ b/files/CHR/talk_紫苑.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87CCE55-A2BD-430D-90E2-9A2BF8B643C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5725889-A55B-43F7-B3F8-FE487DD969CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="525" windowWidth="27990" windowHeight="14415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8355" yWindow="90" windowWidth="20640" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="187">
   <si>
     <t>各キャラクタのランダムセリフ集。指定座標のセリフがあればそちらを優先してしゃべる。</t>
   </si>
@@ -472,12 +472,6 @@
     <t>チュートリアル(タロットカード)</t>
   </si>
   <si>
-    <t>(巡礼者たちは神秘的な力によって一日に一度、奇跡を起こすチャンスがあります。)</t>
-  </si>
-  <si>
-    <t>(心の示すままカードを手に取ってください。)</t>
-  </si>
-  <si>
     <t>チュートリアル(午後)</t>
   </si>
   <si>
@@ -517,9 +511,6 @@
     <t>黒いガラス玉みたいな…</t>
   </si>
   <si>
-    <t>(休息中には精神力を消費して/n生命力を回復できます。)</t>
-  </si>
-  <si>
     <t>(精神力は化け物の親玉のようなものが落とすスピリットポッドを使って回復できます。)</t>
   </si>
   <si>
@@ -533,9 +524,6 @@
   </si>
   <si>
     <t>…いやこの現実ももう充分悪夢なんだけど…</t>
-  </si>
-  <si>
-    <t>(紫苑はわずかに時間を巻き戻す力を持っています。)</t>
   </si>
   <si>
     <t>(全滅の際、または戦闘中に撤退を選択すると、戦闘に突入する前まで戻ることができます。)</t>
@@ -644,6 +632,50 @@
     <rPh sb="14" eb="15">
       <t>キ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(巡礼者たちは神秘的な力によって一日に一度、奇跡を起こすチャンスがあります。)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(心の示すままカードを手に取ってください。)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアル(午後)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(休息中には精神力を消費して生命力を回復できます。)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(その他ステータスの参照やレリクスの装備なども可能です。)</t>
+    <rPh sb="3" eb="4">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアル(休息)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(紫苑はわずかに時間を巻き戻す力を持っているようです。)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアル(ゲームオーバー)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1043,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.75" style="6" customWidth="1"/>
@@ -1803,42 +1835,42 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B96" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B97" t="s">
         <v>175</v>
-      </c>
-      <c r="B97" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" t="s">
         <v>176</v>
-      </c>
-      <c r="B98" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B99" t="s">
         <v>177</v>
-      </c>
-      <c r="B99" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" t="s">
         <v>178</v>
-      </c>
-      <c r="B100" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
@@ -1921,7 +1953,7 @@
         <v>149</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
@@ -1929,147 +1961,155 @@
         <v>149</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="B114" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
+        <v>150</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
+        <v>155</v>
+      </c>
+      <c r="B120" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
+        <v>160</v>
+      </c>
+      <c r="B125" t="s">
         <v>162</v>
-      </c>
-      <c r="B125" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A129" t="s">
-        <v>167</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>160</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
+        <v>164</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>167</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>172</v>
+        <v>164</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B134" s="2"/>
+      <c r="A134" t="s">
+        <v>164</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B135" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/files/CHR/talk_紫苑.xlsx
+++ b/files/CHR/talk_紫苑.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5725889-A55B-43F7-B3F8-FE487DD969CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2EC227-5444-40CA-B18A-6C75C6DF2178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8355" yWindow="90" windowWidth="20640" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7185" yWindow="1050" windowWidth="20640" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,18 +433,6 @@
     <t>もっと味わって食べとけばよかった…</t>
   </si>
   <si>
-    <t>東京(初回)</t>
-  </si>
-  <si>
-    <t>なに…これは生き物…？違う、こっちに近づいてくる…！</t>
-  </si>
-  <si>
-    <t>戦闘突入(初回)</t>
-  </si>
-  <si>
-    <t>何か武器…け、拳銃！？なんでこんな…これで…やってみるしかない…！</t>
-  </si>
-  <si>
     <t>チュートリアル(午前)</t>
   </si>
   <si>
@@ -676,6 +664,22 @@
   </si>
   <si>
     <t>チュートリアル(ゲームオーバー)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なに…これは生き物…？違う、こっちに近づいてくる…！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京(初回)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦闘突入(初回)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>何か武器…け、拳銃！？なんでこんな…これで…やってみるしかない…！</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1835,114 +1839,114 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B97" t="s">
         <v>171</v>
-      </c>
-      <c r="B97" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" t="s">
         <v>172</v>
-      </c>
-      <c r="B98" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B99" t="s">
         <v>173</v>
-      </c>
-      <c r="B99" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" t="s">
         <v>174</v>
-      </c>
-      <c r="B100" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
+        <v>137</v>
+      </c>
+      <c r="B106" t="s">
         <v>141</v>
-      </c>
-      <c r="B106" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B107" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B108" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.4">
@@ -1950,162 +1954,162 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B114" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B116" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
+        <v>146</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
+        <v>151</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
+        <v>160</v>
+      </c>
+      <c r="B134" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.4">

--- a/files/CHR/talk_紫苑.xlsx
+++ b/files/CHR/talk_紫苑.xlsx
@@ -10,12 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2EC227-5444-40CA-B18A-6C75C6DF2178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7185" yWindow="1050" windowWidth="20640" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="20640" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
